--- a/黄冈日程安排0713.xlsx
+++ b/黄冈日程安排0713.xlsx
@@ -8,16 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ants\Desktop\社会实践\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFCAE5B-B79E-4B7C-9893-735AC2D07471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508842B6-8F6C-479A-AA0F-7BBE2393C0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10天日程" sheetId="1" r:id="rId1"/>
     <sheet name="已确定事项" sheetId="2" r:id="rId2"/>
     <sheet name="项目里程碑" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -456,63 +469,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>前往儿童关爱中心，了解爱心班现场情况，开展文具捐赠等活动（步行前往）</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>社区调研建设类产业</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（打车）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">                      
-</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>联系采访市里分管领导（打车）</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>进村入户调查</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>实地调研绿色文旅产业（含红十五军策源地参观）</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>村两委访谈</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 四望镇领导访谈</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>决定应用方向</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -522,10 +482,6 @@
   </si>
   <si>
     <t>文旅宣传角度新媒体和前端</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>特色产业调查</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -563,19 +519,47 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>七里坪长胜街等红色教育参观；人物访谈、团队学习讨论及长征胜利90周年创意活动【雪松，老区，前辈，上科大】</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>九江接站，前往四望镇；（13986545575）           参加爱心班结业式10:00</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>九江住宿</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>儿童关爱中心调查</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>联系采访市里分管领导（打车）（上科大纪念品*2）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>村两委访谈（上科大纪念品*2）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 四望镇领导访谈（上科大纪念品*2）（</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>七里坪长胜街等红色教育参观；人物访谈、团队学习讨论及长征胜利90周年创意活动【雪松，老区，前辈，上科大】（上科大礼物*4）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>前往儿童关爱中心，了解爱心班现场情况，开展文具捐赠等活动（步行前往）（奖状）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>进村入户留守儿童调查（40份礼物）开展讲座，请学校心理老师讲科学教育（劳务费）两次问卷，凸显我们的作用</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>进村农业产业化入户调查（40份礼物）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>社区调研</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>参加爱心班结业式（小礼品）（上科大纪念品张院长马克杯保温）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>特色产业调查（纪念品12份礼物）</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -898,7 +882,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -964,6 +948,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1179,24 +1166,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="13" style="8" customWidth="1"/>
     <col min="2" max="4" width="29" style="8" customWidth="1"/>
-    <col min="5" max="5" width="29.19921875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="29.1875" style="8" customWidth="1"/>
     <col min="6" max="6" width="29" style="8" customWidth="1"/>
     <col min="7" max="7" width="31" style="8" customWidth="1"/>
     <col min="8" max="8" width="27" style="8" customWidth="1"/>
-    <col min="9" max="9" width="26.59765625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="27.59765625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="26.625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="27.625" style="8" customWidth="1"/>
     <col min="11" max="11" width="30" style="8" customWidth="1"/>
-    <col min="12" max="12" width="30.09765625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="30.125" style="8" customWidth="1"/>
     <col min="13" max="13" width="49.5" style="8" customWidth="1"/>
-    <col min="14" max="14" width="54.8984375" style="8" customWidth="1"/>
+    <col min="14" max="14" width="54.875" style="8" customWidth="1"/>
     <col min="15" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="37.950000000000003" customHeight="1">
+    <row r="1" spans="1:14" ht="38" customHeight="1">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1260,31 +1247,31 @@
         <v>128</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>147</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>124</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>131</v>
+        <v>137</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>145</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>129</v>
@@ -1295,13 +1282,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
@@ -1314,10 +1301,10 @@
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="7" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="60" customHeight="1">
@@ -1325,27 +1312,27 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>126</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="18"/>
       <c r="H5" s="16" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="I5" s="18"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="90.75" customHeight="1">
@@ -1357,7 +1344,7 @@
         <v>123</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="17"/>
@@ -1396,7 +1383,7 @@
       <c r="L10" s="7"/>
     </row>
     <row r="11" spans="1:14" ht="70.05" customHeight="1"/>
-    <row r="12" spans="1:14" ht="19.2">
+    <row r="12" spans="1:14" ht="19.149999999999999">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1430,7 +1417,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1635,7 +1622,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="5" width="35" customWidth="1"/>
@@ -1652,7 +1639,7 @@
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
     </row>
-    <row r="2" spans="1:6" ht="15">
+    <row r="2" spans="1:6" ht="13.9">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1660,7 +1647,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="31.95" customHeight="1">
+    <row r="3" spans="1:6" ht="32" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>48</v>
       </c>
@@ -1858,7 +1845,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15">
+    <row r="14" spans="1:6" ht="13.9">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
